--- a/artfynd/A 1793-2025 artfynd.xlsx
+++ b/artfynd/A 1793-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>58026772</v>
       </c>
       <c r="B2" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650001.9369593398</v>
+        <v>650002</v>
       </c>
       <c r="R2" t="n">
-        <v>6590194.040394245</v>
+        <v>6590194</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-04-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -816,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58026797</v>
+        <v>58026773</v>
       </c>
       <c r="B3" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Färentuna, Landholms hage N-ut, 96 m NO vägslutet, Upl</t>
+          <t>Färentuna, Landholms hage N-ut, 107 m NO vägslutet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649999.2844213699</v>
+        <v>650009</v>
       </c>
       <c r="R3" t="n">
-        <v>6590183.746810439</v>
+        <v>6590189</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,24 +878,14 @@
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>75 cm stamomkrets, flerstammig</t>
+          <t>66 cm stamomkrets, tvåstammig</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -957,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58026795</v>
+        <v>58026775</v>
       </c>
       <c r="B4" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1002,14 +967,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Färentuna, Landholms hage N-ut, 94 m NO vägslutet, Upl</t>
+          <t>Färentuna, Landholms hage N-ut, 118 m ONO vägslutet, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649999.405740143</v>
+        <v>650023</v>
       </c>
       <c r="R4" t="n">
-        <v>6590180.695189366</v>
+        <v>6590188</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1039,24 +1004,14 @@
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>66 cm stamomkrets, flerstammig</t>
+          <t>63 cm stamomkrets, grenad stam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1101,12 +1056,7 @@
         <v>58026777</v>
       </c>
       <c r="B5" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650002.6363921976</v>
+        <v>650003</v>
       </c>
       <c r="R5" t="n">
-        <v>6590214.953782249</v>
+        <v>6590215</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1180,19 +1130,9 @@
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-04-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1239,15 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58026781</v>
+        <v>58026780</v>
       </c>
       <c r="B6" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1209,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1284,14 +1219,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Färentuna, Landholms hage N-ut, 125 m NO vägslutet, Upl</t>
+          <t>Färentuna, Landholms hage N-ut, 124 m ONO vägslutet, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650003.9626454294</v>
+        <v>650040</v>
       </c>
       <c r="R6" t="n">
-        <v>6590220.100536981</v>
+        <v>6590173</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1321,24 +1256,14 @@
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-04-25</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>65 cm stamomkrets, &gt; 50 ex, flerstammig</t>
+          <t>42 cm stamomkrets, grenad stam</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,6 +1302,1518 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>58026781</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 125 m NO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>650004</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6590220</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>65 cm stamomkrets, &gt; 50 ex, flerstammig</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>58026783</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 131 m NO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>650030</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6590202</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>73 cm stamomkrets</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>58026784</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 133 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>650054</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6590157</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>54 cm stamomkrets, flerstammig</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Crataegus monogyna</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Crataegus monogyna</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>58026785</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 135 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>650055</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6590162</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>113 cm stamomkrets, grenad stam</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>58026788</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 140 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>650054</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6590178</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>65 cm stamomkrets, grenad stam</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>58026789</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 144 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>650063</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6590168</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>76 cm stamomkrets, grenad stam</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>58026790</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 144 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>650058</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6590179</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>35 cm stamomkrets, grenad stam</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>58026791</v>
+      </c>
+      <c r="B14" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 146 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>650064</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6590172</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>65 cm stamomkrets, grenad stam</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>58026792</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 148 m ONO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>650059</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6590187</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>55 cm stamomkrets, grenad stam</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>58026795</v>
+      </c>
+      <c r="B16" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 94 m NO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>649999</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6590181</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>66 cm stamomkrets, flerstammig</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>58026796</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 95 m NO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>650000</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6590180</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>68 cm stamomkrets</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>58026797</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105120</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mistel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Viscum album</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Färentuna, Landholms hage N-ut, 96 m NO vägslutet, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>649999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6590184</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Färentuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-04-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>75 cm stamomkrets, flerstammig</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>igenvuxen äppelträdgård</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Malus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Svenson, Sture Nordmark</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
